--- a/sample/expected-output.xlsx
+++ b/sample/expected-output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,151 +446,151 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 Oak</t>
+          <t>18 Oak 662x854 CAD-261962</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Finished, no action</t>
+          <t>Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30026196226</t>
+          <t>30023084091</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 Walnut</t>
+          <t>18 Oak 340x777 CAD-230840</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Finished, no action</t>
+          <t>Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30031847710</t>
+          <t>30034453168</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x1200 Oak</t>
+          <t>18 Oak 431x661 CAD-344531</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30031847711</t>
+          <t>30040995108</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x1200 Walnut</t>
+          <t>18 Anth 651x824 CAD-409951</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30044982033</t>
+          <t>30031976178</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tiled Panel 300x600 Oak</t>
+          <t>18 Wte 461x999 CAD-319761</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30055310884</t>
+          <t>30030896419</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tiled Panel 900x900 Grey Stone</t>
+          <t>18 Wte 464x972 CAD-308964</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Edge and drill</t>
+          <t>Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30055310885</t>
+          <t>30061891516</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tiled Panel 900x900 White Stone</t>
+          <t>18 Wte 415x947 CAD-618915</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Edge and drill</t>
+          <t>Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30066471192</t>
+          <t>30060494285</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 Grey Stone</t>
+          <t>18 Anth 442x912 CAD-604942</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30066471193</t>
+          <t>30052872586</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 White Stone</t>
+          <t>18 Oak 625x721 CAD-528725</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -621,18 +621,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>30067353897</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18 Oak 638x683 CAD-673538</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cut, edge and drill</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>30099999999</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tiled Panel 1200x1200 Oak (new line)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tiled Panel (unknown SKU test row)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>SKU NOT FOUND</t>
         </is>

--- a/sample/expected-output.xlsx
+++ b/sample/expected-output.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>Edge and drill</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>Edge and drill</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>Edge and drill</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>Drill</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>Drill</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>Drill</t>
         </is>
       </c>
     </row>

--- a/sample/expected-output.xlsx
+++ b/sample/expected-output.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>next step</t>
+          <t>actions</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Edge and drill</t>
+          <t>58 to Edge and drill</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Edge and drill</t>
+          <t>88 to Edge and drill</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Edge and drill</t>
+          <t>12 to Edge and drill</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>117 to Drill</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>62 to Drill</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>77 to Drill</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>59 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>94 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>22 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>14 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SKU NOT FOUND</t>
+          <t>1 to SKU NOT FOUND</t>
         </is>
       </c>
     </row>

--- a/sample/expected-output.xlsx
+++ b/sample/expected-output.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1 to SKU NOT FOUND</t>
+          <t>SKU NOT FOUND</t>
         </is>
       </c>
     </row>

--- a/sample/expected-output.xlsx
+++ b/sample/expected-output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,11 +429,6 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>actions</t>
         </is>
       </c>
@@ -449,10 +444,7 @@
           <t>18 Oak 662x854 CAD-261962</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>58</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>58 to Edge and drill</t>
         </is>
@@ -469,10 +461,7 @@
           <t>18 Oak 340x777 CAD-230840</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>88</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>88 to Edge and drill</t>
         </is>
@@ -489,10 +478,7 @@
           <t>18 Oak 431x661 CAD-344531</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>12 to Edge and drill</t>
         </is>
@@ -509,10 +495,7 @@
           <t>18 Anth 651x824 CAD-409951</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>117</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>117 to Drill</t>
         </is>
@@ -529,10 +512,7 @@
           <t>18 Wte 461x999 CAD-319761</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>62</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>62 to Drill</t>
         </is>
@@ -549,10 +529,7 @@
           <t>18 Wte 464x972 CAD-308964</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>77</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>77 to Drill</t>
         </is>
@@ -569,10 +546,7 @@
           <t>18 Wte 415x947 CAD-618915</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>59</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>59 to Cut, edge and drill</t>
         </is>
@@ -589,10 +563,7 @@
           <t>18 Anth 442x912 CAD-604942</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>94</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>94 to Cut, edge and drill</t>
         </is>
@@ -609,10 +580,7 @@
           <t>18 Oak 625x721 CAD-528725</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>22 to Cut, edge and drill</t>
         </is>
@@ -629,10 +597,7 @@
           <t>18 Oak 638x683 CAD-673538</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>14</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>14 to Cut, edge and drill</t>
         </is>
@@ -649,10 +614,7 @@
           <t>Tiled Panel (unknown SKU test row)</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>SKU NOT FOUND</t>
         </is>

--- a/sample/expected-output.xlsx
+++ b/sample/expected-output.xlsx
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +42,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,206 +422,211 @@
   </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>30026196225</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>18 Oak 662x854 CAD-261962</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>58 to Edge and drill</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>30023084091</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>18 Oak 340x777 CAD-230840</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>88 to Edge and drill</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>30034453168</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>18 Oak 431x661 CAD-344531</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>12 to Edge and drill</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>30040995108</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>18 Anth 651x824 CAD-409951</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>117 to Drill</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>30031976178</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>18 Wte 461x999 CAD-319761</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>62 to Drill</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>30030896419</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>18 Wte 464x972 CAD-308964</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>77 to Drill</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>30061891516</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>18 Wte 415x947 CAD-618915</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>59 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>30060494285</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>18 Anth 442x912 CAD-604942</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>94 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>30052872586</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>18 Oak 625x721 CAD-528725</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>22 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>30067353897</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>18 Oak 638x683 CAD-673538</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>14 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>30099999999</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Tiled Panel (unknown SKU test row)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>SKU NOT FOUND</t>
         </is>
